--- a/college-posters/data/字段表_211第四批.xlsx
+++ b/college-posters/data/字段表_211第四批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,61 +505,61 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>纺织与新材料、时尚与设计、上海先进制造</t>
+          <t>松江校区：松江大学城主校区；延安路校区：长宁区老校区；图文信息中心：松江校区标志建筑</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>东华大学</t>
+          <t>中国石油大学（华东）</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>松江校区：松江大学城主校区；延安路校区：长宁区老校区；图文信息中心：松江校区标志建筑</t>
+          <t>石油工程、勘查技术与工程、化学工程与工艺、油气储运工程、机械工程、计算机科学与技术</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>东华大学</t>
+          <t>中国石油大学（华东）</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>2023届本科深造率“超45%”（CNUR榜单，具体数值对应不明）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（数值不精确）</t>
         </is>
       </c>
     </row>
@@ -571,112 +571,112 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>石油工程、勘查技术与工程、化学工程与工艺、油气储运工程、机械工程、计算机科学与技术</t>
+          <t>青岛校区：黄岛主校区；东营校区：老校区；图书馆：青岛校区标志建筑</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（华东）</t>
+          <t>南昌大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2023届本科深造率“超45%”（CNUR榜单，具体数值对应不明）</t>
+          <t>材料科学与工程、食品科学与工程、临床医学、计算机科学与技术、法学、新闻学</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核（数值不精确）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（华东）</t>
+          <t>南昌大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>石油石化央企、能源与化工、地质勘探</t>
+          <t>前湖校区：依前湖而建的主校区；青山湖校区：老校区；东湖校区：医学部所在地</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（华东）</t>
+          <t>中国地质大学（北京）</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>青岛校区：黄岛主校区；东营校区：老校区；图书馆：青岛校区标志建筑</t>
+          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、土地资源管理、地理信息科学</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（华东）</t>
+          <t>中国地质大学（北京）</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>学院路校区：北京高校聚集区；地质博物馆：地学科普展馆；主楼：学院路校区标志建筑</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>南昌大学</t>
+          <t>中国矿业大学（北京）</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>材料科学与工程、食品科学与工程、临床医学、计算机科学与技术、法学、新闻学</t>
+          <t>采矿工程、安全工程、矿物加工工程、测绘工程、土木工程、人工智能</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -698,73 +698,73 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>南昌大学</t>
+          <t>中国矿业大学（北京）</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、食品与材料、党政机关与国企</t>
+          <t>学院路校区：北京高校聚集区；沙河校区：昌平新校区；主楼：学院路校区标志建筑</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>南昌大学</t>
+          <t>福州大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>前湖校区：依前湖而建的主校区；青山湖校区：老校区；东湖校区：医学部所在地</t>
+          <t>化学、土木工程、电气工程及其自动化、计算机科学与技术、材料科学与工程、化学工程与工艺</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>南昌大学</t>
+          <t>福州大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>旗山校区：闽侯大学城主校区；铜盘校区：老校区；图书馆：旗山校区标志建筑</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（北京）</t>
+          <t>华南师范大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、土地资源管理、地理信息科学</t>
+          <t>教育学、心理学、物理学、汉语言文学、数学与应用数学、计算机科学与技术</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -786,73 +786,73 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（北京）</t>
+          <t>华南师范大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>地质勘探与资源、测绘与地理信息、能源与环境</t>
+          <t>石牌校区：天河区老校区；大学城校区：番禺大学城；南海校区：佛山南海校区</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（北京）</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>学院路校区：北京高校聚集区；地质博物馆：地学科普展馆；主楼：学院路校区标志建筑</t>
+          <t>车辆工程、机械设计制造及其自动化、电气工程及其自动化、计算机科学与技术、信息管理与信息系统、土木工程</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（北京）</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>屯溪路校区：合肥老校区；翡翠湖校区：主校区；宣城校区：皖南校区</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>中国矿业大学（北京）</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>采矿工程、安全工程、矿物加工工程、测绘工程、土木工程、人工智能</t>
+          <t>林学、风景园林、园林、生态学、木材科学与工程、水土保持与荒漠化防治</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -874,506 +874,66 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中国矿业大学（北京）</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>煤炭与能源央企、安全与应急管理、土木与测绘</t>
+          <t>清华东路校区：海淀主校区；鹫峰林场：京郊实习林场；校园绿化：花木繁茂的校园</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国矿业大学（北京）</t>
+          <t>华北电力大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>学院路校区：北京高校聚集区；沙河校区：昌平新校区；主楼：学院路校区标志建筑</t>
+          <t>电气工程及其自动化、能源与动力工程、新能源科学与工程、核工程与核技术、自动化、计算机科学与技术</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国矿业大学（北京）</t>
+          <t>华北电力大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>北京校区：昌平主校区；保定校区：河北保定校区；主楼：北京校区标志建筑</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>福州大学</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>化学、土木工程、电气工程及其自动化、计算机科学与技术、材料科学与工程、化学工程与工艺</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>福州大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与制造、建筑与土木工程、福建本地企业</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>福州大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>旗山校区：闽侯大学城主校区；铜盘校区：老校区；图书馆：旗山校区标志建筑</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>福州大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>华南师范大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>教育学、心理学、物理学、汉语言文学、数学与应用数学、计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>华南师范大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、粤港澳大湾区企业、党政机关与事业单位</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>华南师范大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>石牌校区：天河区老校区；大学城校区：番禺大学城；南海校区：佛山南海校区</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>华南师范大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>合肥工业大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>车辆工程、机械设计制造及其自动化、电气工程及其自动化、计算机科学与技术、信息管理与信息系统、土木工程</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>合肥工业大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>汽车与先进制造、电子信息与互联网、长三角企业</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>合肥工业大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>屯溪路校区：合肥老校区；翡翠湖校区：主校区；宣城校区：皖南校区</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>合肥工业大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>北京林业大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>林学、风景园林、园林、生态学、木材科学与工程、水土保持与荒漠化防治</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>北京林业大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>园林设计与生态、林业与自然资源、环保与科研</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>北京林业大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>清华东路校区：海淀主校区；鹫峰林场：京郊实习林场；校园绿化：花木繁茂的校园</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>北京林业大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>华北电力大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>电气工程及其自动化、能源与动力工程、新能源科学与工程、核工程与核技术、自动化、计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>华北电力大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>电网与发电企业、新能源与核电、电力设计与装备</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>华北电力大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>北京校区：昌平主校区；保定校区：河北保定校区；主楼：北京校区标志建筑</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>华北电力大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1937,9 +1497,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2062,12 +1622,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2695,9 +2255,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2380,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3453,9 +3013,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3138,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4211,9 +3771,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4336,12 +3896,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4969,9 +4529,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5094,12 +4654,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5727,9 +5287,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5412,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6485,9 +6045,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6170,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7243,9 +6803,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7368,12 +6928,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8001,9 +7561,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8126,12 +7686,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8759,9 +8319,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8444,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
